--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92576266241</v>
+        <v>46157.93121442814</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93121442814</v>
+        <v>46157.93187104732</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93187104732</v>
+        <v>46157.93407794016</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93407794016</v>
+        <v>46157.93725693369</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93725693369</v>
+        <v>46158.28223178869</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28223178869</v>
+        <v>46158.29713363402</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29713363402</v>
+        <v>46158.29823413216</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29823413216</v>
+        <v>46158.33394236893</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33394236893</v>
+        <v>46158.36863993468</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36863993468</v>
+        <v>46158.37294982559</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
